--- a/Labs/TermProject/CS133JS_TermProject_Rubric.xlsx
+++ b/Labs/TermProject/CS133JS_TermProject_Rubric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brian/Repos/CS133JS-CourseMaterials/Labs/TermProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DataCard/Repos/CS133JS-Repos/CS133JS-CourseMaterials/Labs/TermProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DDE3B5-3A92-8F4D-B284-D5609BBAE9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E289EF-568B-3E47-84AD-4C19FE32075C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12800" yWindow="600" windowWidth="13440" windowHeight="15420" activeTab="1" xr2:uid="{9702CE45-50CE-F14F-802C-E5FE921247A2}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t>Criteria</t>
   </si>
@@ -103,6 +103,15 @@
   </si>
   <si>
     <t xml:space="preserve">Excellent work! Your project is well done and meets all the requirements. </t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Everything works</t>
+  </si>
+  <si>
+    <t>Good</t>
   </si>
 </sst>
 </file>
@@ -168,17 +177,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -657,24 +666,24 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="37" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
@@ -700,7 +709,7 @@
       <c r="D5" s="2"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="17">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -710,9 +719,11 @@
       <c r="D6">
         <v>15</v>
       </c>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -722,9 +733,11 @@
       <c r="D7">
         <v>15</v>
       </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -734,9 +747,11 @@
       <c r="D8">
         <v>15</v>
       </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -746,9 +761,11 @@
       <c r="D9">
         <v>15</v>
       </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -758,9 +775,11 @@
       <c r="D10">
         <v>15</v>
       </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -770,7 +789,9 @@
       <c r="D11">
         <v>15</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
@@ -778,7 +799,7 @@
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="17">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -788,9 +809,11 @@
       <c r="D13">
         <v>5</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -800,9 +823,11 @@
       <c r="D14">
         <v>60</v>
       </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="17">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -812,9 +837,11 @@
       <c r="D15">
         <v>20</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -824,9 +851,11 @@
       <c r="D16">
         <v>20</v>
       </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="F16" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="17">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -836,7 +865,9 @@
       <c r="D17">
         <v>5</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="1:6">
       <c r="F18" s="4"/>
@@ -859,12 +890,12 @@
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="7">
         <f>D19/C19</f>
         <v>1</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
